--- a/samples/入力シート_記入例.xlsx
+++ b/samples/入力シート_記入例.xlsx
@@ -287,6 +287,21 @@
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>セル内改行で箇条書き</t>
+      </text>
+    </comment>
+    <comment ref="Z3" authorId="0" shapeId="0">
+      <text>
+        <t>この欄だけでも可。見出しは付けずにそのまま印字します</t>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="0" shapeId="0">
+      <text>
+        <t>任意。志望の動機に続けて印字します</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0" shapeId="0">
+      <text>
+        <t>任意。最後に続けて印字します</t>
       </text>
     </comment>
   </commentList>
@@ -610,9 +625,9 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="34" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="34" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="26" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
@@ -827,17 +842,17 @@
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
+          <t>志望の動機</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
           <t>希望の職種</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>アピールポイント</t>
-        </is>
-      </c>
-      <c r="AB3" s="5" t="inlineStr">
-        <is>
-          <t>志望の動機</t>
         </is>
       </c>
       <c r="AC3" s="5" t="inlineStr">
@@ -994,17 +1009,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>motivation</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>desired_job</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>appeal</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>motivation</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1123,17 +1138,17 @@
       </c>
       <c r="Z5" s="7" t="inlineStr">
         <is>
+          <t>実習で金属を削って形にする面白さを知り、ものづくりの現場で働きたいと考えるようになりました。貴社は多品種少量の精密加工に強みがあり、若いうちから幅広い機械に触れられると伺っています。学校で学んだ機械加工の基礎を早く現場で活かし、確かな技術を身につけて長く貢献したいと思い志望しました。</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
           <t>機械加工・生産技術</t>
         </is>
       </c>
-      <c r="AA5" s="7" t="inlineStr">
+      <c r="AB5" s="7" t="inlineStr">
         <is>
           <t>旋盤とフライス盤の実習で、寸法公差を守る段取りと確認を身につけました。分からないことはその場で質問し、最後まで丁寧にやり切ることを大切にしています。</t>
-        </is>
-      </c>
-      <c r="AB5" s="7" t="inlineStr">
-        <is>
-          <t>実習で金属を削って形にする面白さを知り、ものづくりの現場で働きたいと考えるようになりました。貴社は多品種少量の精密加工に強みがあり、若いうちから幅広い機械に触れられると伺っています。学校で学んだ機械加工の基礎を早く現場で活かし、確かな技術を身につけて長く貢献したいと思い志望しました。</t>
         </is>
       </c>
       <c r="AC5" s="8" t="n"/>
@@ -1240,17 +1255,17 @@
       </c>
       <c r="Z6" s="7" t="inlineStr">
         <is>
+          <t>工場見学で、たくさんの部品が計画どおりに動いて製品になる仕組みに興味を持ちました。簿記と情報の授業で学んだことを活かして、現場を支える仕事に就きたいと考え志望しました。</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
           <t>生産管理・事務</t>
         </is>
       </c>
-      <c r="AA6" s="7" t="inlineStr">
+      <c r="AB6" s="7" t="inlineStr">
         <is>
           <t>3年間、無遅刻無欠席で続けてきました。人と話すことが好きで、部活動では初心者の後輩の指導を担当しました。</t>
-        </is>
-      </c>
-      <c r="AB6" s="7" t="inlineStr">
-        <is>
-          <t>工場見学で、たくさんの部品が計画どおりに動いて製品になる仕組みに興味を持ちました。簿記と情報の授業で学んだことを活かして、現場を支える仕事に就きたいと考え志望しました。</t>
         </is>
       </c>
       <c r="AC6" s="8" t="n"/>
@@ -1332,17 +1347,17 @@
       </c>
       <c r="Z7" s="7" t="inlineStr">
         <is>
+          <t>インターンシップで貴社の現場を見学し、機械を扱う正確さに憧れました。基礎から学んで一人前になりたいと思い志望しました。</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
           <t>機械オペレーター</t>
         </is>
       </c>
-      <c r="AA7" s="7" t="inlineStr">
+      <c r="AB7" s="7" t="inlineStr">
         <is>
           <t>部活動で主将を務め、練習メニューを考えて部員をまとめました。体力に自信があります。</t>
-        </is>
-      </c>
-      <c r="AB7" s="7" t="inlineStr">
-        <is>
-          <t>インターンシップで貴社の現場を見学し、機械を扱う正確さに憧れました。基礎から学んで一人前になりたいと思い志望しました。</t>
         </is>
       </c>
       <c r="AC7" s="8" t="n"/>

--- a/samples/入力シート_記入例.xlsx
+++ b/samples/入力シート_記入例.xlsx
@@ -1095,7 +1095,7 @@
       <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>電気工事士第二種</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>危険物取扱者乙4</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>技能検定3級 機械加工（普通旋盤作業）</t>
+          <t>技能検定　機械加工（普通旋盤作業）3級</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
@@ -1321,7 +1321,7 @@
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>小型フォークリフト運転特別教育修了</t>
+          <t>小型フォークリフト運転特別教育講習修了</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2887,12 +2887,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>英検5級</t>
+          <t>実用英語検定5級</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定5級</t>
+          <t>実用英語検定5級</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
@@ -2900,12 +2900,12 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>英検4級</t>
+          <t>実用英語検定4級</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定4級</t>
+          <t>実用英語検定4級</t>
         </is>
       </c>
       <c r="C5" s="12" t="n"/>
@@ -2913,12 +2913,12 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>英検3級</t>
+          <t>実用英語検定3級</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定3級</t>
+          <t>実用英語検定3級</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
@@ -2926,12 +2926,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>英検準2級</t>
+          <t>実用英語検定準２級</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準2級</t>
+          <t>実用英語検定準２級</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
@@ -2939,12 +2939,12 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>英検2級</t>
+          <t>実用英語検定2級</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定2級</t>
+          <t>実用英語検定2級</t>
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
@@ -2952,12 +2952,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>英検準1級</t>
+          <t>実用英語検定1級</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準1級</t>
+          <t>実用英語検定1級</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -2965,12 +2965,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定3級</t>
+          <t>日本漢字能力検定4級</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定3級</t>
+          <t>日本漢字能力検定4級</t>
         </is>
       </c>
       <c r="C10" s="12" t="n"/>
@@ -2978,12 +2978,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定準2級</t>
+          <t>日本漢字能力検定3級</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準2級</t>
+          <t>日本漢字能力検定3級</t>
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
@@ -2991,12 +2991,12 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定2級</t>
+          <t>日本漢字能力検定準2級</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定2級</t>
+          <t>日本漢字能力検定準2級</t>
         </is>
       </c>
       <c r="C12" s="12" t="n"/>
@@ -3004,12 +3004,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>漢検4級</t>
+          <t>日本漢字能力検定2級</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定4級</t>
+          <t>日本漢字能力検定2級</t>
         </is>
       </c>
       <c r="C13" s="12" t="n"/>
@@ -3017,12 +3017,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>漢検3級</t>
+          <t>計算技術検定1級</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定3級</t>
+          <t>計算技術検定1級</t>
         </is>
       </c>
       <c r="C14" s="12" t="n"/>
@@ -3030,12 +3030,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>漢検準2級</t>
+          <t>計算技術検定2級</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定準2級</t>
+          <t>計算技術検定2級</t>
         </is>
       </c>
       <c r="C15" s="12" t="n"/>
@@ -3043,12 +3043,12 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>漢検2級</t>
+          <t>計算技術検定3級</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定2級</t>
+          <t>計算技術検定3級</t>
         </is>
       </c>
       <c r="C16" s="12" t="n"/>
@@ -3056,12 +3056,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>数検3級</t>
+          <t>計算技術検定4級</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>実用数学技能検定3級</t>
+          <t>計算技術検定4級</t>
         </is>
       </c>
       <c r="C17" s="12" t="n"/>
@@ -3069,12 +3069,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>数検準2級</t>
+          <t>情報技術検定1級</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>実用数学技能検定準2級</t>
+          <t>情報技術検定1級</t>
         </is>
       </c>
       <c r="C18" s="12" t="n"/>
@@ -3082,12 +3082,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>乙4</t>
+          <t>情報技術検定2級</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>情報技術検定2級</t>
         </is>
       </c>
       <c r="C19" s="12" t="n"/>
@@ -3095,12 +3095,12 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>危険物乙4</t>
+          <t>情報技術検定3級</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>情報技術検定3級</t>
         </is>
       </c>
       <c r="C20" s="12" t="n"/>
@@ -3108,12 +3108,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種4類</t>
+          <t>初級CAD検定</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>初級CAD検定</t>
         </is>
       </c>
       <c r="C21" s="12" t="n"/>
@@ -3121,12 +3121,12 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>電工2種</t>
+          <t>基礎製図検定</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>基礎製図検定</t>
         </is>
       </c>
       <c r="C22" s="12" t="n"/>
@@ -3134,12 +3134,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>第2種電気工事士</t>
+          <t>機械製図検定</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>機械製図検定</t>
         </is>
       </c>
       <c r="C23" s="12" t="n"/>
@@ -3147,12 +3147,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>電気工事士2種</t>
+          <t>色彩検定３級</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>色彩検定３級</t>
         </is>
       </c>
       <c r="C24" s="12" t="n"/>
@@ -3160,12 +3160,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>ガス溶接</t>
+          <t>色彩検定２級</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>ガス溶接技能講習修了</t>
+          <t>色彩検定２級</t>
         </is>
       </c>
       <c r="C25" s="12" t="n"/>
@@ -3173,12 +3173,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接</t>
+          <t>色彩検定UC級</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接等特別教育修了</t>
+          <t>色彩検定UC級</t>
         </is>
       </c>
       <c r="C26" s="12" t="n"/>
@@ -3186,12 +3186,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接特別教育修了</t>
+          <t>QC検定4級</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接等特別教育修了</t>
+          <t>QC検定4級</t>
         </is>
       </c>
       <c r="C27" s="12" t="n"/>
@@ -3199,12 +3199,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>フォークリフト</t>
+          <t>QC検定3級</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>フォークリフト運転技能講習修了</t>
+          <t>QC検定3級</t>
         </is>
       </c>
       <c r="C28" s="12" t="n"/>
@@ -3212,12 +3212,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>小型フォークリフト</t>
+          <t>日本語ワープロ検定2級</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>小型フォークリフト運転特別教育修了</t>
+          <t>日本語ワープロ検定2級</t>
         </is>
       </c>
       <c r="C29" s="12" t="n"/>
@@ -3225,12 +3225,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>玉掛け</t>
+          <t>日本語ワープロ検定準2級</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>玉掛け技能講習修了</t>
+          <t>日本語ワープロ検定準2級</t>
         </is>
       </c>
       <c r="C30" s="12" t="n"/>
@@ -3238,12 +3238,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>普通免許</t>
+          <t>日本語ワープロ検定3級</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>普通自動車第一種運転免許</t>
+          <t>日本語ワープロ検定3級</t>
         </is>
       </c>
       <c r="C31" s="12" t="n"/>
@@ -3251,12 +3251,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>普通自動車免許</t>
+          <t>日本語ワープロ検定4級</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>普通自動車第一種運転免許</t>
+          <t>日本語ワープロ検定4級</t>
         </is>
       </c>
       <c r="C32" s="12" t="n"/>
@@ -3264,12 +3264,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>原付</t>
+          <t>情報処理技能検定(表計算)4級</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>原動機付自転車運転免許</t>
+          <t>情報処理技能検定(表計算)4級</t>
         </is>
       </c>
       <c r="C33" s="12" t="n"/>
@@ -3277,12 +3277,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>基礎製図検定</t>
+          <t>文書デザイン検定4級</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>基礎製図検定</t>
+          <t>文書デザイン検定4級</t>
         </is>
       </c>
       <c r="C34" s="12" t="n"/>
@@ -3290,12 +3290,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>機械製図検定</t>
+          <t>プレゼンテーション作成検定3級</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>機械製図検定</t>
+          <t>プレゼンテーション作成検定3級</t>
         </is>
       </c>
       <c r="C35" s="12" t="n"/>
@@ -3303,12 +3303,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定3級</t>
+          <t>プレゼンテーション作成検定4級</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定3級</t>
+          <t>プレゼンテーション作成検定4級</t>
         </is>
       </c>
       <c r="C36" s="12" t="n"/>
@@ -3316,12 +3316,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定2級</t>
+          <t>パソコンスピード認定1級</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定2級</t>
+          <t>パソコンスピード認定1級</t>
         </is>
       </c>
       <c r="C37" s="12" t="n"/>
@@ -3329,12 +3329,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定3級</t>
+          <t>パソコンスピード認定2級</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定3級</t>
+          <t>パソコンスピード認定2級</t>
         </is>
       </c>
       <c r="C38" s="12" t="n"/>
@@ -3342,12 +3342,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定2級</t>
+          <t>パソコンスピード認定3級</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定2級</t>
+          <t>パソコンスピード認定3級</t>
         </is>
       </c>
       <c r="C39" s="12" t="n"/>
@@ -3355,12 +3355,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>技能検定3級</t>
+          <t>パソコンスピード認定4級</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>技能検定3級</t>
+          <t>パソコンスピード認定4級</t>
         </is>
       </c>
       <c r="C40" s="12" t="n"/>
@@ -3368,12 +3368,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>初級CAD検定</t>
+          <t>パソコンスピード認定5級</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>初級CAD検定</t>
+          <t>パソコンスピード認定5級</t>
         </is>
       </c>
       <c r="C41" s="12" t="n"/>
@@ -3381,12 +3381,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>QC検定3級</t>
+          <t>電気工事士第一種</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>品質管理検定3級</t>
+          <t>電気工事士第一種</t>
         </is>
       </c>
       <c r="C42" s="12" t="n"/>
@@ -3394,12 +3394,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>QC検定4級</t>
+          <t>電気工事士第二種</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>品質管理検定4級</t>
+          <t>電気工事士第二種</t>
         </is>
       </c>
       <c r="C43" s="12" t="n"/>
@@ -3407,12 +3407,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>日本語ワープロ検定3級</t>
+          <t>危険物取扱者乙1</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>日本語ワープロ検定3級</t>
+          <t>危険物取扱者乙1</t>
         </is>
       </c>
       <c r="C44" s="12" t="n"/>
@@ -3420,12 +3420,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>情報処理技能検定(表計算)4級</t>
+          <t>危険物取扱者乙2</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>情報処理技能検定試験 表計算4級</t>
+          <t>危険物取扱者乙2</t>
         </is>
       </c>
       <c r="C45" s="12" t="n"/>
@@ -3433,12 +3433,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>硬筆書写技能検定4級</t>
+          <t>危険物取扱者乙3</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>硬筆書写技能検定4級</t>
+          <t>危険物取扱者乙3</t>
         </is>
       </c>
       <c r="C46" s="12" t="n"/>
@@ -3446,15 +3446,353 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>簿記3級</t>
+          <t>危険物取扱者乙4</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>日商簿記検定3級</t>
+          <t>危険物取扱者乙4</t>
         </is>
       </c>
       <c r="C47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙5</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙5</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙6</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙6</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者丙</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者丙</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>ガス溶接技能講習修了</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>ガス溶接技能講習修了</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>ボイラー取扱技能講習修了</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>ボイラー取扱技能講習修了</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>ア－ク溶接安全衛生教育修了</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>ア－ク溶接安全衛生教育修了</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>小型フォークリフト運転特別教育講習修了</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>小型フォークリフト運転特別教育講習修了</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>二級ボイラー技士2級</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>二級ボイラー技士2級</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）2級</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）2級</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）3級</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）3級</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）2級</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）2級</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）3級</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）3級</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２V</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２V</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ｎ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ｎ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２H</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２H</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SＮ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SＮ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書T－1Ｆ</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書T－1Ｆ</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SA－2Ｆ</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SA－2Ｆ</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>第二級デジタル通信</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>第二級デジタル通信</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターゴールド</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターゴールド</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターシルバー</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターシルバー</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターブロンズ</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターブロンズ</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>フォークリフト運転技能講習</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>フォークリフト運転技能講習</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>玉掛け技能講習</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>玉掛け技能講習</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>硬筆書写技能検定4級</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>硬筆書写技能検定4級</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3518,22 +3856,30 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>3-2-2 近畿花子 英検2級 2025/6/8</t>
+          <t>3-2-2 近畿花子 実用英語検定2級 2025/6/8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>3-2-3 泉州一郎 乙4 令和7年3月14日</t>
+          <t>3-2-3 泉州一郎 危険物取扱者乙4 令和7年3月14日</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>3-2-2 近畿花子 色彩検定３級 令和7年7月13日</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>3-2-1 佐野太郎 アーク溶接安全衛生教育修了 2025/9/5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>

--- a/samples/入力シート_記入例.xlsx
+++ b/samples/入力シート_記入例.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="入力" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="設定" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="資格マスタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="資格取込" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="使い方" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="反映項目" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="資格マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="資格取込" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="使い方" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入力'!$A$3:$AG$44</definedName>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +132,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -2845,6 +2849,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>反映項目（PDFに出す項目を選びます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B列を「○」にした項目だけをPDFに書き込みます。「×」にすると、入力してあってもその欄は空欄のまま印刷されます（入力シートの値は消えません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>反映する（○／×）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ふりがな（氏名）</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>name_kana</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>生年月日・満○歳</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>ふりがな（住所）</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>address_kana</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>連絡先（「同上」を含む）</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>資格等</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>licenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>校内外の諸活動</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>志望の動機</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>motivation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>希望の職種</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>desired_job</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>アピールポイント</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>appeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>職歴</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3799,7 +4091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4471,169 +4763,245 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>■ このファイルについて</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>「入力」シートは 1行＝1生徒 の名列順です。クラス全員分をまとめて入力できます。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>入力して保存したあと python build_pdf.py を実行すると、生徒ごとの履歴書PDFが 出力/ にできます。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
+      <c r="A4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>■ 手順</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>1. 「入力」シートの黄色いセルに、名列順で入力する（氏名が空の行はPDFを作りません）。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>2. 「設定」シートの基準日を確認する（満○歳の計算に使います）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>3. python build_pdf.py            … 全員分のPDFを作る</t>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>3. このファイルを保存して閉じる（開いたままでも作れます）。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   python build_pdf.py --no 3     … No.3 の生徒だけ</t>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>4. 「履歴書PDF作成」を起動して、青い【PDF作成】ボタンを押す。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   python build_pdf.py --merge 3年2組_履歴書.pdf … 全員を1つのPDFにまとめる（印刷用）</t>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Windows … 履歴書PDF作成.bat をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   python watch.py                … 保存するたび自動で作り直す</t>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   macOS  … 履歴書PDF作成.command をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 画面では「全員／No.指定／氏名で絞り込み」「1つのPDFにまとめる」「自動更新」も選べます。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>■ 自動で入る項目</t>
-        </is>
-      </c>
+      <c r="A13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>■ コマンドで使う場合（画面を使わないとき）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python build_pdf.py            … 全員分のPDFを作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python build_pdf.py --no 3     … No.3 の生徒だけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python build_pdf.py --merge 3年2組_履歴書.pdf … 全員を1つのPDFにまとめる（印刷用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python watch.py                … 保存するたび自動で作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>■ PDFに出す項目を選ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>「反映項目」シートで、項目ごとに ○（出す）／×（出さない）を選べます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>×にした欄は、入力してあってもPDFでは空欄のままになります（入力シートの値は消えません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>画面（履歴書PDF作成）のチェックボックスでも、その場で切り替えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>■ 自動で入る項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
           <t>・満○歳 … 生年月日と基準日から自動計算します。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>・元号（昭和／平成／令和） … 生年月日から自動判定します。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>・連絡先 … 空欄なら「同上」と印字します。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>・郵便番号 … 7桁の数字だけでも 123-4567 の形に整えます。</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>・資格の取得年月 … 西暦で入力しても和暦（例: 令和6年6月）で印字します。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>■ 注意</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>・4行目は非表示のキー行です。読み取りに使うので、消したり並べ替えたりしないでください。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>・生徒を増やすときは、5行目以降の行をコピーして貼り付けてください。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>・列を増やすときは、4行目に同じ書き方のキー（license.7.name など）も入れてください。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>・写真は用紙の「写真をはる位置」に貼ってください（PDFには合成しません）。</t>
         </is>
